--- a/Test_Cases/03_Add_Resource/Add_Resource_Test_Cases.xlsx
+++ b/Test_Cases/03_Add_Resource/Add_Resource_Test_Cases.xlsx
@@ -1,24 +1,20 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Add Resource Test Cases" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution" sheetId="2" state="visible" r:id="rId2"/>
-  </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Add Resource Test Cases'!$A$1:$K$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Execution'!$A$1:$H$49</definedName>
-  </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
+  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
+  <AppVersion>3.1</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties">
+  <dc:creator xmlns:dc="http://purl.org/dc/elements/1.1/">openpyxl</dc:creator>
+  <dcterms:created xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xsi:type="dcterms:W3CDTF">2026-08-15T15:40:47Z</dcterms:created>
+  <dcterms:modified xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xsi:type="dcterms:W3CDTF">2026-08-15T15:40:47Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="2">
@@ -151,7 +147,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -434,7 +430,26 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Add Resource Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution" sheetId="2" state="visible" r:id="rId2"/>
+  </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Add Resource Test Cases'!$A$1:$K$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Execution'!$A$1:$H$49</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3425,7 +3440,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3499,14 +3514,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3521,14 +3552,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3543,14 +3590,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3565,14 +3628,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3587,14 +3666,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3609,14 +3704,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -3631,14 +3742,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -3653,14 +3780,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -3675,14 +3818,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3697,14 +3856,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3719,14 +3894,34 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
+          <t>Not Applicable - By Design</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Chapter/Topic field is permanently disabled in the Create form, so neither its required-validation nor its selector component can be exercised.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>APP-DEFECT-CHAPTERTOPIC</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>REMOVED from automation (add-resource.cy.js). Chapter &amp; Topic is auto-filled and disabled in the Create form BY DESIGN - a custom asset is always created against the lesson topic the teacher is on, so there is nothing to select and nothing that can be left empty. This test case describes a selector the product deliberately does not offer. TC-AR-014 covers the real behaviour (field always populated, never blocks submit).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3741,14 +3936,34 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
+          <t>Not Applicable - By Design</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Chapter/Topic field is permanently disabled in the Create form, so neither its required-validation nor its selector component can be exercised.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>APP-DEFECT-CHAPTERTOPIC</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>REMOVED from automation (add-resource.cy.js). Chapter &amp; Topic is auto-filled and disabled in the Create form BY DESIGN - a custom asset is always created against the lesson topic the teacher is on, so there is nothing to select and nothing that can be left empty. This test case describes a selector the product deliberately does not offer. TC-AR-014 covers the real behaviour (field always populated, never blocks submit).</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3763,14 +3978,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3785,14 +4016,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3807,14 +4054,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3829,14 +4092,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3851,14 +4130,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3873,14 +4168,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3895,14 +4206,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3917,14 +4244,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -3939,14 +4282,30 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -3961,14 +4320,30 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -3983,14 +4358,30 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -4005,14 +4396,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -4027,14 +4434,30 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -4049,14 +4472,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Playlist count did not increase after Add to playlist. The chosen Library search result was already attached from earlier runs, and the backend silently de-duplicates re-attaching an already-attached resource.</t>
+        </is>
+      </c>
       <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Not a product defect - test data issue. Test hardcoded search-result index 3, which prior runs consumed. Fixed to select an unattached result at runtime (LibraryPage.firstUnattachedResultIndex). Awaiting re-verification.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -4071,14 +4510,30 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -4093,14 +4548,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -4115,14 +4586,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -4137,14 +4624,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -4159,14 +4662,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -4181,14 +4700,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Not Automatable - Manual</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>OUT OF SCOPE for automation - removed from add-resource.cy.js. Verifying a real DropIt transfer needs a second physical device, or writing directly into the app Firestore pairing collection. Execute manually. Automated coverage is limited to the pairing UI itself (TC-AR-031).</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -4203,14 +4734,26 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Not Automatable - Manual</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>OUT OF SCOPE for automation - removed from add-resource.cy.js. Verifying a real DropIt transfer needs a second physical device, or writing directly into the app Firestore pairing collection. Execute manually. Automated coverage is limited to the pairing UI itself (TC-AR-031).</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -4225,14 +4768,26 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Not Automatable - Manual</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>OUT OF SCOPE for automation - removed from add-resource.cy.js. Verifying a real DropIt transfer needs a second physical device, or writing directly into the app Firestore pairing collection. Execute manually. Automated coverage is limited to the pairing UI itself (TC-AR-031).</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -4247,14 +4802,30 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -4269,14 +4840,30 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -4291,14 +4878,30 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -4313,14 +4916,30 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -4335,14 +4954,30 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -4357,14 +4992,30 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4379,14 +5030,30 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -4401,14 +5068,30 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4423,14 +5106,30 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4445,14 +5144,30 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4467,14 +5182,30 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4489,14 +5220,30 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4511,14 +5258,30 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4533,14 +5296,30 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Behaved as expected.</t>
+        </is>
+      </c>
       <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Automation</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Automated - cypress/e2e/03-add-resource/add-resource.cy.js</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H49"/>
